--- a/output/accuracy_logistic.xlsx
+++ b/output/accuracy_logistic.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,43 +474,1143 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4177</v>
+        <v>0.07989599999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>3.63</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>2.19</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>1.27</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>6.78</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>7.52</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>8.17</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>8.74</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.093824</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00027246</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.869999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00026128</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00012917</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.949999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0030126</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.003033</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.026472</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.359999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.035054</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.017559</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.018242</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.022424</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.035052</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.369999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.051833</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>19</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.06555</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.090991</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>21</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.032573</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>22</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.047171</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>23</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.071477</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.093818</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>26</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.11438</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>27</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.13558</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>28</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.082194</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>29</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.099942</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>30</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.10811</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/accuracy_logistic.xlsx
+++ b/output/accuracy_logistic.xlsx
@@ -477,40 +477,40 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07989599999999999</v>
+        <v>0.010287</v>
       </c>
       <c r="D2" t="n">
-        <v>3.63</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="n">
-        <v>2.19</v>
+        <v>1.07</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="n">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
       <c r="H2" t="n">
-        <v>1.27</v>
+        <v>3.31</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18</v>
+        <v>7.54</v>
       </c>
       <c r="J2" t="n">
-        <v>6.78</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>7.52</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>8.17</v>
+        <v>5.9</v>
       </c>
       <c r="M2" t="n">
-        <v>8.74</v>
+        <v>6.63</v>
       </c>
       <c r="N2" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="3">
@@ -521,40 +521,40 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.093824</v>
+        <v>0.0096808</v>
       </c>
       <c r="D3" t="n">
-        <v>4.95</v>
+        <v>1.72</v>
       </c>
       <c r="E3" t="n">
-        <v>3.92</v>
+        <v>0.84</v>
       </c>
       <c r="F3" t="n">
-        <v>2.98</v>
+        <v>3.71</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>0.25</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34</v>
+        <v>3.53</v>
       </c>
       <c r="I3" t="n">
-        <v>0.63</v>
+        <v>7.75</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>6.21</v>
       </c>
       <c r="K3" t="n">
-        <v>4.31</v>
+        <v>5.52</v>
       </c>
       <c r="L3" t="n">
-        <v>4.85</v>
+        <v>6.12</v>
       </c>
       <c r="M3" t="n">
-        <v>5.35</v>
+        <v>6.84</v>
       </c>
       <c r="N3" t="n">
-        <v>3.41</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
@@ -565,40 +565,40 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00027246</v>
+        <v>0.009461499999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>11.18</v>
+        <v>1.67</v>
       </c>
       <c r="E4" t="n">
-        <v>11.18</v>
+        <v>0.89</v>
       </c>
       <c r="F4" t="n">
-        <v>11.18</v>
+        <v>3.76</v>
       </c>
       <c r="G4" t="n">
-        <v>11.18</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="n">
-        <v>11.18</v>
+        <v>3.48</v>
       </c>
       <c r="I4" t="n">
-        <v>11.18</v>
+        <v>7.71</v>
       </c>
       <c r="J4" t="n">
-        <v>7.91</v>
+        <v>6.17</v>
       </c>
       <c r="K4" t="n">
-        <v>7.91</v>
+        <v>5.47</v>
       </c>
       <c r="L4" t="n">
-        <v>7.91</v>
+        <v>6.07</v>
       </c>
       <c r="M4" t="n">
-        <v>7.91</v>
+        <v>6.8</v>
       </c>
       <c r="N4" t="n">
-        <v>9.869999999999999</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="5">
@@ -609,40 +609,40 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00026128</v>
+        <v>0.011321</v>
       </c>
       <c r="D5" t="n">
-        <v>11.23</v>
+        <v>1.92</v>
       </c>
       <c r="E5" t="n">
-        <v>11.23</v>
+        <v>0.63</v>
       </c>
       <c r="F5" t="n">
-        <v>11.23</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>11.23</v>
+        <v>0.04</v>
       </c>
       <c r="H5" t="n">
-        <v>11.23</v>
+        <v>3.73</v>
       </c>
       <c r="I5" t="n">
-        <v>11.23</v>
+        <v>7.94</v>
       </c>
       <c r="J5" t="n">
-        <v>7.96</v>
+        <v>6.41</v>
       </c>
       <c r="K5" t="n">
-        <v>7.96</v>
+        <v>5.72</v>
       </c>
       <c r="L5" t="n">
-        <v>7.96</v>
+        <v>6.31</v>
       </c>
       <c r="M5" t="n">
-        <v>7.96</v>
+        <v>7.04</v>
       </c>
       <c r="N5" t="n">
-        <v>9.92</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="6">
@@ -653,40 +653,40 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00012917</v>
+        <v>0.018801</v>
       </c>
       <c r="D6" t="n">
-        <v>11.26</v>
+        <v>2.26</v>
       </c>
       <c r="E6" t="n">
-        <v>11.26</v>
+        <v>0.29</v>
       </c>
       <c r="F6" t="n">
-        <v>11.26</v>
+        <v>3.14</v>
       </c>
       <c r="G6" t="n">
-        <v>11.26</v>
+        <v>0.3</v>
       </c>
       <c r="H6" t="n">
-        <v>11.26</v>
+        <v>4.06</v>
       </c>
       <c r="I6" t="n">
-        <v>11.26</v>
+        <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>7.99</v>
+        <v>6.73</v>
       </c>
       <c r="K6" t="n">
-        <v>7.99</v>
+        <v>6.04</v>
       </c>
       <c r="L6" t="n">
-        <v>7.99</v>
+        <v>6.63</v>
       </c>
       <c r="M6" t="n">
-        <v>7.99</v>
+        <v>7.36</v>
       </c>
       <c r="N6" t="n">
-        <v>9.949999999999999</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="7">
@@ -697,40 +697,40 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0030126</v>
+        <v>0.022282</v>
       </c>
       <c r="D7" t="n">
-        <v>10.99</v>
+        <v>2.21</v>
       </c>
       <c r="E7" t="n">
-        <v>10.99</v>
+        <v>0.34</v>
       </c>
       <c r="F7" t="n">
-        <v>10.99</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>10.99</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
-        <v>10.99</v>
+        <v>4.01</v>
       </c>
       <c r="I7" t="n">
-        <v>10.99</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>7.71</v>
+        <v>6.68</v>
       </c>
       <c r="K7" t="n">
-        <v>7.71</v>
+        <v>5.99</v>
       </c>
       <c r="L7" t="n">
-        <v>7.71</v>
+        <v>6.58</v>
       </c>
       <c r="M7" t="n">
-        <v>7.71</v>
+        <v>7.31</v>
       </c>
       <c r="N7" t="n">
-        <v>9.68</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="8">
@@ -741,40 +741,40 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003033</v>
+        <v>0.0068734</v>
       </c>
       <c r="D8" t="n">
-        <v>11.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>11.06</v>
+        <v>2.04</v>
       </c>
       <c r="F8" t="n">
-        <v>11.06</v>
+        <v>5.05</v>
       </c>
       <c r="G8" t="n">
-        <v>11.06</v>
+        <v>1.61</v>
       </c>
       <c r="H8" t="n">
-        <v>11.06</v>
+        <v>2.18</v>
       </c>
       <c r="I8" t="n">
-        <v>11.06</v>
+        <v>6.43</v>
       </c>
       <c r="J8" t="n">
-        <v>7.78</v>
+        <v>4.85</v>
       </c>
       <c r="K8" t="n">
-        <v>7.78</v>
+        <v>4.13</v>
       </c>
       <c r="L8" t="n">
-        <v>7.78</v>
+        <v>4.73</v>
       </c>
       <c r="M8" t="n">
-        <v>7.78</v>
+        <v>5.46</v>
       </c>
       <c r="N8" t="n">
-        <v>9.75</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="9">
@@ -785,40 +785,40 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>0.026472</v>
+        <v>0.0062788</v>
       </c>
       <c r="D9" t="n">
-        <v>10.71</v>
+        <v>0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>10.69</v>
+        <v>3.37</v>
       </c>
       <c r="F9" t="n">
-        <v>10.68</v>
+        <v>6.58</v>
       </c>
       <c r="G9" t="n">
-        <v>10.68</v>
+        <v>3.22</v>
       </c>
       <c r="H9" t="n">
-        <v>10.68</v>
+        <v>0.53</v>
       </c>
       <c r="I9" t="n">
-        <v>10.67</v>
+        <v>4.77</v>
       </c>
       <c r="J9" t="n">
-        <v>7.38</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>7.38</v>
+        <v>2.31</v>
       </c>
       <c r="L9" t="n">
-        <v>7.38</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>7.38</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>9.359999999999999</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="10">
@@ -829,40 +829,40 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>0.035054</v>
+        <v>0.0073483</v>
       </c>
       <c r="D10" t="n">
-        <v>10.06</v>
+        <v>0.63</v>
       </c>
       <c r="E10" t="n">
-        <v>9.94</v>
+        <v>3.64</v>
       </c>
       <c r="F10" t="n">
-        <v>9.85</v>
+        <v>6.91</v>
       </c>
       <c r="G10" t="n">
-        <v>9.779999999999999</v>
+        <v>3.58</v>
       </c>
       <c r="H10" t="n">
-        <v>9.73</v>
+        <v>0.14</v>
       </c>
       <c r="I10" t="n">
-        <v>9.69</v>
+        <v>4.37</v>
       </c>
       <c r="J10" t="n">
-        <v>6.33</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
-        <v>6.3</v>
+        <v>1.86</v>
       </c>
       <c r="L10" t="n">
-        <v>6.28</v>
+        <v>2.41</v>
       </c>
       <c r="M10" t="n">
-        <v>6.27</v>
+        <v>3.11</v>
       </c>
       <c r="N10" t="n">
-        <v>8.42</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="11">
@@ -873,40 +873,40 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>0.017559</v>
+        <v>0.0072622</v>
       </c>
       <c r="D11" t="n">
-        <v>10.38</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>10.32</v>
+        <v>2.95</v>
       </c>
       <c r="F11" t="n">
-        <v>10.28</v>
+        <v>6.14</v>
       </c>
       <c r="G11" t="n">
-        <v>10.25</v>
+        <v>2.79</v>
       </c>
       <c r="H11" t="n">
-        <v>10.23</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>10.22</v>
+        <v>5.17</v>
       </c>
       <c r="J11" t="n">
-        <v>6.9</v>
+        <v>3.51</v>
       </c>
       <c r="K11" t="n">
-        <v>6.89</v>
+        <v>2.73</v>
       </c>
       <c r="L11" t="n">
-        <v>6.89</v>
+        <v>3.29</v>
       </c>
       <c r="M11" t="n">
-        <v>6.88</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>8.92</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="12">
@@ -917,40 +917,40 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.018242</v>
+        <v>0.010753</v>
       </c>
       <c r="D12" t="n">
-        <v>10.58</v>
+        <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>10.55</v>
+        <v>3.26</v>
       </c>
       <c r="F12" t="n">
-        <v>10.53</v>
+        <v>6.5</v>
       </c>
       <c r="G12" t="n">
-        <v>10.51</v>
+        <v>3.18</v>
       </c>
       <c r="H12" t="n">
-        <v>10.5</v>
+        <v>0.54</v>
       </c>
       <c r="I12" t="n">
-        <v>10.49</v>
+        <v>4.77</v>
       </c>
       <c r="J12" t="n">
-        <v>7.19</v>
+        <v>3.07</v>
       </c>
       <c r="K12" t="n">
-        <v>7.19</v>
+        <v>2.27</v>
       </c>
       <c r="L12" t="n">
-        <v>7.18</v>
+        <v>2.83</v>
       </c>
       <c r="M12" t="n">
-        <v>7.18</v>
+        <v>3.53</v>
       </c>
       <c r="N12" t="n">
-        <v>9.19</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="13">
@@ -961,40 +961,40 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.022424</v>
+        <v>0.026739</v>
       </c>
       <c r="D13" t="n">
-        <v>10.05</v>
+        <v>1.06</v>
       </c>
       <c r="E13" t="n">
-        <v>9.960000000000001</v>
+        <v>4.29</v>
       </c>
       <c r="F13" t="n">
-        <v>9.890000000000001</v>
+        <v>7.76</v>
       </c>
       <c r="G13" t="n">
-        <v>9.84</v>
+        <v>4.58</v>
       </c>
       <c r="H13" t="n">
-        <v>9.800000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="I13" t="n">
-        <v>9.77</v>
+        <v>3.19</v>
       </c>
       <c r="J13" t="n">
-        <v>6.42</v>
+        <v>1.36</v>
       </c>
       <c r="K13" t="n">
-        <v>6.41</v>
+        <v>0.44</v>
       </c>
       <c r="L13" t="n">
-        <v>6.39</v>
+        <v>0.92</v>
       </c>
       <c r="M13" t="n">
-        <v>6.38</v>
+        <v>1.56</v>
       </c>
       <c r="N13" t="n">
-        <v>8.49</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="14">
@@ -1005,40 +1005,40 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.035052</v>
+        <v>0.043749</v>
       </c>
       <c r="D14" t="n">
-        <v>10.02</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
-        <v>9.9</v>
+        <v>5.28</v>
       </c>
       <c r="F14" t="n">
-        <v>9.81</v>
+        <v>9.02</v>
       </c>
       <c r="G14" t="n">
-        <v>9.73</v>
+        <v>6.01</v>
       </c>
       <c r="H14" t="n">
-        <v>9.68</v>
+        <v>2.54</v>
       </c>
       <c r="I14" t="n">
-        <v>9.640000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="J14" t="n">
-        <v>6.27</v>
+        <v>0.52</v>
       </c>
       <c r="K14" t="n">
-        <v>6.24</v>
+        <v>1.61</v>
       </c>
       <c r="L14" t="n">
-        <v>6.22</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>6.21</v>
+        <v>0.72</v>
       </c>
       <c r="N14" t="n">
-        <v>8.369999999999999</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="15">
@@ -1049,40 +1049,40 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>0.051833</v>
+        <v>0.038166</v>
       </c>
       <c r="D15" t="n">
-        <v>9.56</v>
+        <v>2.34</v>
       </c>
       <c r="E15" t="n">
-        <v>9.380000000000001</v>
+        <v>6.09</v>
       </c>
       <c r="F15" t="n">
-        <v>9.23</v>
+        <v>10.13</v>
       </c>
       <c r="G15" t="n">
-        <v>9.109999999999999</v>
+        <v>7.36</v>
       </c>
       <c r="H15" t="n">
-        <v>9.02</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>8.94</v>
+        <v>0.24</v>
       </c>
       <c r="J15" t="n">
-        <v>5.52</v>
+        <v>2.55</v>
       </c>
       <c r="K15" t="n">
-        <v>5.47</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>5.43</v>
+        <v>3.77</v>
       </c>
       <c r="M15" t="n">
-        <v>5.4</v>
+        <v>3.44</v>
       </c>
       <c r="N15" t="n">
-        <v>7.71</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="16">
@@ -1093,40 +1093,40 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.06555</v>
+        <v>0.038201</v>
       </c>
       <c r="D16" t="n">
-        <v>9.69</v>
+        <v>2.37</v>
       </c>
       <c r="E16" t="n">
-        <v>9.49</v>
+        <v>6.13</v>
       </c>
       <c r="F16" t="n">
-        <v>9.33</v>
+        <v>10.18</v>
       </c>
       <c r="G16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.42</v>
       </c>
       <c r="H16" t="n">
-        <v>9.09</v>
+        <v>4.17</v>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>0.32</v>
       </c>
       <c r="J16" t="n">
-        <v>5.57</v>
+        <v>2.64</v>
       </c>
       <c r="K16" t="n">
-        <v>5.51</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>5.46</v>
+        <v>3.88</v>
       </c>
       <c r="M16" t="n">
-        <v>5.42</v>
+        <v>3.56</v>
       </c>
       <c r="N16" t="n">
-        <v>7.78</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="17">
@@ -1137,40 +1137,40 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.090991</v>
+        <v>0.040115</v>
       </c>
       <c r="D17" t="n">
-        <v>9.18</v>
+        <v>2.57</v>
       </c>
       <c r="E17" t="n">
-        <v>8.84</v>
+        <v>6.41</v>
       </c>
       <c r="F17" t="n">
-        <v>8.550000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="G17" t="n">
-        <v>8.31</v>
+        <v>7.83</v>
       </c>
       <c r="H17" t="n">
-        <v>8.09</v>
+        <v>4.63</v>
       </c>
       <c r="I17" t="n">
-        <v>7.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>4.35</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.21</v>
+        <v>4.63</v>
       </c>
       <c r="L17" t="n">
-        <v>4.09</v>
+        <v>4.56</v>
       </c>
       <c r="M17" t="n">
-        <v>3.99</v>
+        <v>4.29</v>
       </c>
       <c r="N17" t="n">
-        <v>6.75</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="18">
@@ -1181,40 +1181,40 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.032573</v>
+        <v>0.033513</v>
       </c>
       <c r="D18" t="n">
-        <v>9.85</v>
+        <v>2.37</v>
       </c>
       <c r="E18" t="n">
-        <v>9.68</v>
+        <v>6.15</v>
       </c>
       <c r="F18" t="n">
-        <v>9.539999999999999</v>
+        <v>10.22</v>
       </c>
       <c r="G18" t="n">
-        <v>9.42</v>
+        <v>7.48</v>
       </c>
       <c r="H18" t="n">
-        <v>9.32</v>
+        <v>4.24</v>
       </c>
       <c r="I18" t="n">
-        <v>9.24</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
-        <v>5.82</v>
+        <v>2.75</v>
       </c>
       <c r="K18" t="n">
-        <v>5.76</v>
+        <v>4.13</v>
       </c>
       <c r="L18" t="n">
-        <v>5.72</v>
+        <v>4.03</v>
       </c>
       <c r="M18" t="n">
-        <v>5.68</v>
+        <v>3.73</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="19">
@@ -1225,40 +1225,40 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.047171</v>
+        <v>0.034349</v>
       </c>
       <c r="D19" t="n">
-        <v>9.34</v>
+        <v>2.25</v>
       </c>
       <c r="E19" t="n">
-        <v>9.050000000000001</v>
+        <v>5.99</v>
       </c>
       <c r="F19" t="n">
-        <v>8.800000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="G19" t="n">
-        <v>8.58</v>
+        <v>7.24</v>
       </c>
       <c r="H19" t="n">
-        <v>8.390000000000001</v>
+        <v>3.99</v>
       </c>
       <c r="I19" t="n">
-        <v>8.23</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>4.69</v>
+        <v>2.43</v>
       </c>
       <c r="K19" t="n">
-        <v>4.57</v>
+        <v>3.78</v>
       </c>
       <c r="L19" t="n">
-        <v>4.46</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>4.36</v>
+        <v>3.33</v>
       </c>
       <c r="N19" t="n">
-        <v>7.05</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="20">
@@ -1269,40 +1269,40 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.071477</v>
+        <v>0.038815</v>
       </c>
       <c r="D20" t="n">
-        <v>9.17</v>
+        <v>1.95</v>
       </c>
       <c r="E20" t="n">
-        <v>8.82</v>
+        <v>5.61</v>
       </c>
       <c r="F20" t="n">
-        <v>8.51</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>8.23</v>
+        <v>6.72</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>3.41</v>
       </c>
       <c r="I20" t="n">
-        <v>7.79</v>
+        <v>0.49</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>1.74</v>
       </c>
       <c r="K20" t="n">
-        <v>4.03</v>
+        <v>3.02</v>
       </c>
       <c r="L20" t="n">
-        <v>3.88</v>
+        <v>2.83</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>2.46</v>
       </c>
       <c r="N20" t="n">
-        <v>6.64</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="21">
@@ -1313,40 +1313,40 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.093818</v>
+        <v>0.039966</v>
       </c>
       <c r="D21" t="n">
-        <v>9.039999999999999</v>
+        <v>1.81</v>
       </c>
       <c r="E21" t="n">
-        <v>8.69</v>
+        <v>5.43</v>
       </c>
       <c r="F21" t="n">
-        <v>8.380000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="G21" t="n">
-        <v>8.1</v>
+        <v>6.47</v>
       </c>
       <c r="H21" t="n">
-        <v>7.87</v>
+        <v>3.14</v>
       </c>
       <c r="I21" t="n">
-        <v>7.66</v>
+        <v>0.78</v>
       </c>
       <c r="J21" t="n">
-        <v>4.06</v>
+        <v>1.42</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>2.67</v>
       </c>
       <c r="L21" t="n">
-        <v>3.76</v>
+        <v>2.46</v>
       </c>
       <c r="M21" t="n">
-        <v>3.63</v>
+        <v>2.07</v>
       </c>
       <c r="N21" t="n">
-        <v>6.51</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="22">
@@ -1357,40 +1357,40 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1261</v>
+        <v>0.04003</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>1.78</v>
       </c>
       <c r="E22" t="n">
-        <v>8.6</v>
+        <v>5.39</v>
       </c>
       <c r="F22" t="n">
-        <v>8.23</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>7.91</v>
+        <v>6.42</v>
       </c>
       <c r="H22" t="n">
-        <v>7.63</v>
+        <v>3.08</v>
       </c>
       <c r="I22" t="n">
-        <v>7.38</v>
+        <v>0.84</v>
       </c>
       <c r="J22" t="n">
-        <v>3.74</v>
+        <v>1.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.54</v>
+        <v>2.59</v>
       </c>
       <c r="L22" t="n">
-        <v>3.36</v>
+        <v>2.38</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="N22" t="n">
-        <v>6.26</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="23">
@@ -1401,40 +1401,40 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.11438</v>
+        <v>0.040637</v>
       </c>
       <c r="D23" t="n">
-        <v>9.69</v>
+        <v>1.89</v>
       </c>
       <c r="E23" t="n">
-        <v>9.43</v>
+        <v>5.53</v>
       </c>
       <c r="F23" t="n">
-        <v>9.210000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="G23" t="n">
-        <v>9.01</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>8.85</v>
+        <v>3.28</v>
       </c>
       <c r="I23" t="n">
-        <v>8.710000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="J23" t="n">
-        <v>5.22</v>
+        <v>1.58</v>
       </c>
       <c r="K23" t="n">
-        <v>5.11</v>
+        <v>2.84</v>
       </c>
       <c r="L23" t="n">
-        <v>5.02</v>
+        <v>2.64</v>
       </c>
       <c r="M23" t="n">
-        <v>4.94</v>
+        <v>2.25</v>
       </c>
       <c r="N23" t="n">
-        <v>7.52</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="24">
@@ -1445,40 +1445,40 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.13558</v>
+        <v>0.048526</v>
       </c>
       <c r="D24" t="n">
-        <v>9.32</v>
+        <v>2.1</v>
       </c>
       <c r="E24" t="n">
-        <v>8.960000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="F24" t="n">
-        <v>8.640000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>8.369999999999999</v>
+        <v>6.98</v>
       </c>
       <c r="H24" t="n">
-        <v>8.119999999999999</v>
+        <v>3.69</v>
       </c>
       <c r="I24" t="n">
-        <v>7.91</v>
+        <v>0.19</v>
       </c>
       <c r="J24" t="n">
-        <v>4.32</v>
+        <v>2.07</v>
       </c>
       <c r="K24" t="n">
-        <v>4.16</v>
+        <v>3.38</v>
       </c>
       <c r="L24" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N24" t="n">
         <v>4.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6.77</v>
       </c>
     </row>
     <row r="25">
@@ -1489,40 +1489,40 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.082194</v>
+        <v>0.048526</v>
       </c>
       <c r="D25" t="n">
-        <v>8.26</v>
+        <v>2.1</v>
       </c>
       <c r="E25" t="n">
-        <v>7.78</v>
+        <v>5.8</v>
       </c>
       <c r="F25" t="n">
-        <v>7.35</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>6.96</v>
+        <v>6.97</v>
       </c>
       <c r="H25" t="n">
-        <v>6.61</v>
+        <v>3.69</v>
       </c>
       <c r="I25" t="n">
-        <v>6.31</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
-        <v>2.57</v>
+        <v>2.07</v>
       </c>
       <c r="K25" t="n">
-        <v>2.31</v>
+        <v>3.37</v>
       </c>
       <c r="L25" t="n">
-        <v>2.09</v>
+        <v>3.21</v>
       </c>
       <c r="M25" t="n">
-        <v>1.88</v>
+        <v>2.86</v>
       </c>
       <c r="N25" t="n">
-        <v>5.21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1533,40 +1533,40 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.099942</v>
+        <v>0.060548</v>
       </c>
       <c r="D26" t="n">
-        <v>8.279999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="E26" t="n">
-        <v>7.7</v>
+        <v>6.27</v>
       </c>
       <c r="F26" t="n">
-        <v>7.16</v>
+        <v>10.36</v>
       </c>
       <c r="G26" t="n">
-        <v>6.68</v>
+        <v>7.62</v>
       </c>
       <c r="H26" t="n">
-        <v>6.24</v>
+        <v>4.39</v>
       </c>
       <c r="I26" t="n">
-        <v>5.85</v>
+        <v>0.54</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>2.89</v>
       </c>
       <c r="K26" t="n">
-        <v>1.66</v>
+        <v>4.28</v>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>4.18</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>3.88</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="27">
@@ -1577,40 +1577,40 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.10811</v>
+        <v>0.07278800000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>8.1</v>
+        <v>2.63</v>
       </c>
       <c r="E27" t="n">
-        <v>7.58</v>
+        <v>6.49</v>
       </c>
       <c r="F27" t="n">
-        <v>7.12</v>
+        <v>10.64</v>
       </c>
       <c r="G27" t="n">
-        <v>6.71</v>
+        <v>7.95</v>
       </c>
       <c r="H27" t="n">
-        <v>6.34</v>
+        <v>4.76</v>
       </c>
       <c r="I27" t="n">
-        <v>6.01</v>
+        <v>0.95</v>
       </c>
       <c r="J27" t="n">
-        <v>2.23</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>1.95</v>
+        <v>4.79</v>
       </c>
       <c r="L27" t="n">
-        <v>1.71</v>
+        <v>4.73</v>
       </c>
       <c r="M27" t="n">
-        <v>1.49</v>
+        <v>4.47</v>
       </c>
       <c r="N27" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/accuracy_logistic.xlsx
+++ b/output/accuracy_logistic.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,43 +474,43 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>0.010287</v>
+        <v>0.020785</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>18.31</v>
       </c>
       <c r="E2" t="n">
-        <v>1.07</v>
+        <v>30.84</v>
       </c>
       <c r="F2" t="n">
-        <v>3.95</v>
+        <v>36.81</v>
       </c>
       <c r="G2" t="n">
-        <v>0.48</v>
+        <v>53.63</v>
       </c>
       <c r="H2" t="n">
-        <v>3.31</v>
+        <v>58.35</v>
       </c>
       <c r="I2" t="n">
-        <v>7.54</v>
+        <v>63.26</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>65.62</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>5.9</v>
+        <v>71.27</v>
       </c>
       <c r="M2" t="n">
-        <v>6.63</v>
+        <v>71.78</v>
       </c>
       <c r="N2" t="n">
-        <v>4.17</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="3">
@@ -518,43 +518,43 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0096808</v>
+        <v>0.1489</v>
       </c>
       <c r="D3" t="n">
-        <v>1.72</v>
+        <v>77.13</v>
       </c>
       <c r="E3" t="n">
-        <v>0.84</v>
+        <v>57.08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.71</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25</v>
+        <v>14.83</v>
       </c>
       <c r="H3" t="n">
-        <v>3.53</v>
+        <v>7.42</v>
       </c>
       <c r="I3" t="n">
-        <v>7.75</v>
+        <v>1.48</v>
       </c>
       <c r="J3" t="n">
-        <v>6.21</v>
+        <v>4.31</v>
       </c>
       <c r="K3" t="n">
-        <v>5.52</v>
+        <v>14.17</v>
       </c>
       <c r="L3" t="n">
-        <v>6.12</v>
+        <v>14.17</v>
       </c>
       <c r="M3" t="n">
-        <v>6.84</v>
+        <v>12.82</v>
       </c>
       <c r="N3" t="n">
-        <v>4.25</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="4">
@@ -562,43 +562,43 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009461499999999999</v>
+        <v>0.15261</v>
       </c>
       <c r="D4" t="n">
-        <v>1.67</v>
+        <v>76.06</v>
       </c>
       <c r="E4" t="n">
-        <v>0.89</v>
+        <v>56.12</v>
       </c>
       <c r="F4" t="n">
-        <v>3.76</v>
+        <v>49.09</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>14.13</v>
       </c>
       <c r="H4" t="n">
-        <v>3.48</v>
+        <v>6.77</v>
       </c>
       <c r="I4" t="n">
-        <v>7.71</v>
+        <v>2.08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.17</v>
+        <v>4.89</v>
       </c>
       <c r="K4" t="n">
-        <v>5.47</v>
+        <v>14.7</v>
       </c>
       <c r="L4" t="n">
-        <v>6.07</v>
+        <v>14.7</v>
       </c>
       <c r="M4" t="n">
-        <v>6.8</v>
+        <v>13.36</v>
       </c>
       <c r="N4" t="n">
-        <v>4.23</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="5">
@@ -606,43 +606,43 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>0.011321</v>
+        <v>0.058318</v>
       </c>
       <c r="D5" t="n">
-        <v>1.92</v>
+        <v>30.91</v>
       </c>
       <c r="E5" t="n">
-        <v>0.63</v>
+        <v>16.09</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>10.86</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04</v>
+        <v>15.13</v>
       </c>
       <c r="H5" t="n">
-        <v>3.73</v>
+        <v>20.61</v>
       </c>
       <c r="I5" t="n">
-        <v>7.94</v>
+        <v>27.18</v>
       </c>
       <c r="J5" t="n">
-        <v>6.41</v>
+        <v>29.28</v>
       </c>
       <c r="K5" t="n">
-        <v>5.72</v>
+        <v>36.57</v>
       </c>
       <c r="L5" t="n">
-        <v>6.31</v>
+        <v>36.57</v>
       </c>
       <c r="M5" t="n">
-        <v>7.04</v>
+        <v>35.57</v>
       </c>
       <c r="N5" t="n">
-        <v>4.32</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="6">
@@ -650,43 +650,43 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>0.018801</v>
+        <v>0.058473</v>
       </c>
       <c r="D6" t="n">
-        <v>2.26</v>
+        <v>29.76</v>
       </c>
       <c r="E6" t="n">
-        <v>0.29</v>
+        <v>15.07</v>
       </c>
       <c r="F6" t="n">
-        <v>3.14</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3</v>
+        <v>15.88</v>
       </c>
       <c r="H6" t="n">
-        <v>4.06</v>
+        <v>21.31</v>
       </c>
       <c r="I6" t="n">
-        <v>8.26</v>
+        <v>27.82</v>
       </c>
       <c r="J6" t="n">
-        <v>6.73</v>
+        <v>29.9</v>
       </c>
       <c r="K6" t="n">
-        <v>6.04</v>
+        <v>37.13</v>
       </c>
       <c r="L6" t="n">
-        <v>6.63</v>
+        <v>37.13</v>
       </c>
       <c r="M6" t="n">
-        <v>7.36</v>
+        <v>36.14</v>
       </c>
       <c r="N6" t="n">
-        <v>4.51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -694,43 +694,43 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>0.022282</v>
+        <v>0.058693</v>
       </c>
       <c r="D7" t="n">
-        <v>2.21</v>
+        <v>28.64</v>
       </c>
       <c r="E7" t="n">
-        <v>0.34</v>
+        <v>14.08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>8.94</v>
       </c>
       <c r="G7" t="n">
-        <v>0.25</v>
+        <v>16.61</v>
       </c>
       <c r="H7" t="n">
-        <v>4.01</v>
+        <v>21.99</v>
       </c>
       <c r="I7" t="n">
-        <v>8.210000000000001</v>
+        <v>28.45</v>
       </c>
       <c r="J7" t="n">
-        <v>6.68</v>
+        <v>30.51</v>
       </c>
       <c r="K7" t="n">
-        <v>5.99</v>
+        <v>37.67</v>
       </c>
       <c r="L7" t="n">
-        <v>6.58</v>
+        <v>37.67</v>
       </c>
       <c r="M7" t="n">
-        <v>7.31</v>
+        <v>36.69</v>
       </c>
       <c r="N7" t="n">
-        <v>4.48</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="8">
@@ -738,43 +738,43 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0068734</v>
+        <v>0.058209</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6899999999999999</v>
+        <v>28.65</v>
       </c>
       <c r="E8" t="n">
-        <v>2.04</v>
+        <v>14.08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.05</v>
+        <v>8.94</v>
       </c>
       <c r="G8" t="n">
-        <v>1.61</v>
+        <v>16.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.18</v>
+        <v>21.98</v>
       </c>
       <c r="I8" t="n">
-        <v>6.43</v>
+        <v>28.45</v>
       </c>
       <c r="J8" t="n">
-        <v>4.85</v>
+        <v>30.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.13</v>
+        <v>37.67</v>
       </c>
       <c r="L8" t="n">
-        <v>4.73</v>
+        <v>37.67</v>
       </c>
       <c r="M8" t="n">
-        <v>5.46</v>
+        <v>36.69</v>
       </c>
       <c r="N8" t="n">
-        <v>3.72</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="9">
@@ -782,43 +782,43 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0062788</v>
+        <v>0.057775</v>
       </c>
       <c r="D9" t="n">
-        <v>0.42</v>
+        <v>29.37</v>
       </c>
       <c r="E9" t="n">
-        <v>3.37</v>
+        <v>14.73</v>
       </c>
       <c r="F9" t="n">
-        <v>6.58</v>
+        <v>9.56</v>
       </c>
       <c r="G9" t="n">
-        <v>3.22</v>
+        <v>16.13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.53</v>
+        <v>21.54</v>
       </c>
       <c r="I9" t="n">
-        <v>4.77</v>
+        <v>28.04</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>30.11</v>
       </c>
       <c r="K9" t="n">
-        <v>2.31</v>
+        <v>37.32</v>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>37.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>36.33</v>
       </c>
       <c r="N9" t="n">
-        <v>3.08</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="10">
@@ -826,43 +826,43 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0073483</v>
+        <v>0.05827</v>
       </c>
       <c r="D10" t="n">
-        <v>0.63</v>
+        <v>29.28</v>
       </c>
       <c r="E10" t="n">
-        <v>3.64</v>
+        <v>14.64</v>
       </c>
       <c r="F10" t="n">
-        <v>6.91</v>
+        <v>9.48</v>
       </c>
       <c r="G10" t="n">
-        <v>3.58</v>
+        <v>16.19</v>
       </c>
       <c r="H10" t="n">
-        <v>0.14</v>
+        <v>21.6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.37</v>
+        <v>28.09</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>30.16</v>
       </c>
       <c r="K10" t="n">
-        <v>1.86</v>
+        <v>37.36</v>
       </c>
       <c r="L10" t="n">
-        <v>2.41</v>
+        <v>37.36</v>
       </c>
       <c r="M10" t="n">
-        <v>3.11</v>
+        <v>36.38</v>
       </c>
       <c r="N10" t="n">
-        <v>2.93</v>
+        <v>26.05</v>
       </c>
     </row>
     <row r="11">
@@ -870,43 +870,43 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0072622</v>
+        <v>0.057986</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03</v>
+        <v>29.66</v>
       </c>
       <c r="E11" t="n">
-        <v>2.95</v>
+        <v>14.98</v>
       </c>
       <c r="F11" t="n">
-        <v>6.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>2.79</v>
+        <v>15.95</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9399999999999999</v>
+        <v>21.37</v>
       </c>
       <c r="I11" t="n">
-        <v>5.17</v>
+        <v>27.88</v>
       </c>
       <c r="J11" t="n">
-        <v>3.51</v>
+        <v>29.96</v>
       </c>
       <c r="K11" t="n">
-        <v>2.73</v>
+        <v>37.18</v>
       </c>
       <c r="L11" t="n">
-        <v>3.29</v>
+        <v>37.18</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>36.19</v>
       </c>
       <c r="N11" t="n">
-        <v>3.16</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="12">
@@ -914,43 +914,43 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>0.010753</v>
+        <v>0.00095341</v>
       </c>
       <c r="D12" t="n">
-        <v>0.27</v>
+        <v>14.44</v>
       </c>
       <c r="E12" t="n">
-        <v>3.26</v>
+        <v>1.48</v>
       </c>
       <c r="F12" t="n">
-        <v>6.5</v>
+        <v>3.09</v>
       </c>
       <c r="G12" t="n">
-        <v>3.18</v>
+        <v>25.81</v>
       </c>
       <c r="H12" t="n">
-        <v>0.54</v>
+        <v>30.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.77</v>
+        <v>36.35</v>
       </c>
       <c r="J12" t="n">
-        <v>3.07</v>
+        <v>38.18</v>
       </c>
       <c r="K12" t="n">
-        <v>2.27</v>
+        <v>44.55</v>
       </c>
       <c r="L12" t="n">
-        <v>2.83</v>
+        <v>44.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.53</v>
+        <v>43.68</v>
       </c>
       <c r="N12" t="n">
-        <v>3.02</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="13">
@@ -958,43 +958,43 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>0.026739</v>
+        <v>0.0011694</v>
       </c>
       <c r="D13" t="n">
-        <v>1.06</v>
+        <v>15.34</v>
       </c>
       <c r="E13" t="n">
-        <v>4.29</v>
+        <v>2.28</v>
       </c>
       <c r="F13" t="n">
-        <v>7.76</v>
+        <v>2.32</v>
       </c>
       <c r="G13" t="n">
-        <v>4.58</v>
+        <v>25.23</v>
       </c>
       <c r="H13" t="n">
-        <v>0.96</v>
+        <v>30.05</v>
       </c>
       <c r="I13" t="n">
-        <v>3.19</v>
+        <v>35.85</v>
       </c>
       <c r="J13" t="n">
-        <v>1.36</v>
+        <v>37.69</v>
       </c>
       <c r="K13" t="n">
-        <v>0.44</v>
+        <v>44.11</v>
       </c>
       <c r="L13" t="n">
-        <v>0.92</v>
+        <v>44.11</v>
       </c>
       <c r="M13" t="n">
-        <v>1.56</v>
+        <v>43.24</v>
       </c>
       <c r="N13" t="n">
-        <v>2.61</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="14">
@@ -1002,615 +1002,43 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>0.043749</v>
+        <v>0.0011615</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>5.28</v>
+        <v>0.21</v>
       </c>
       <c r="F14" t="n">
-        <v>9.02</v>
+        <v>4.31</v>
       </c>
       <c r="G14" t="n">
-        <v>6.01</v>
+        <v>26.75</v>
       </c>
       <c r="H14" t="n">
-        <v>2.54</v>
+        <v>31.47</v>
       </c>
       <c r="I14" t="n">
-        <v>1.51</v>
+        <v>37.15</v>
       </c>
       <c r="J14" t="n">
-        <v>0.52</v>
+        <v>38.95</v>
       </c>
       <c r="K14" t="n">
-        <v>1.61</v>
+        <v>45.25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>45.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0.72</v>
+        <v>44.39</v>
       </c>
       <c r="N14" t="n">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.038166</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>19</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.038201</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E16" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.47</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>20</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.040115</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E17" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>21</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.033513</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E18" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>22</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.034349</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>23</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.038815</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="F20" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>24</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.039966</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="F21" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="n">
-        <v>25</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.04003</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="F22" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="n">
-        <v>26</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.040637</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="F23" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="n">
-        <v>27</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.048526</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F24" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="n">
-        <v>28</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.048526</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F25" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="L25" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="n">
-        <v>29</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.060548</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="F26" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="L26" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.69</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="n">
-        <v>30</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.07278800000000001</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E27" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="F27" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="G27" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.08</v>
+        <v>28.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/accuracy_logistic.xlsx
+++ b/output/accuracy_logistic.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,43 +474,43 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.020785</v>
+        <v>0.0039935</v>
       </c>
       <c r="D2" t="n">
-        <v>18.31</v>
+        <v>3.85</v>
       </c>
       <c r="E2" t="n">
-        <v>30.84</v>
+        <v>5.14</v>
       </c>
       <c r="F2" t="n">
-        <v>36.81</v>
+        <v>6.96</v>
       </c>
       <c r="G2" t="n">
-        <v>53.63</v>
+        <v>10.53</v>
       </c>
       <c r="H2" t="n">
-        <v>58.35</v>
+        <v>11.37</v>
       </c>
       <c r="I2" t="n">
-        <v>63.26</v>
+        <v>13.32</v>
       </c>
       <c r="J2" t="n">
-        <v>65.62</v>
+        <v>15.6</v>
       </c>
       <c r="K2" t="n">
-        <v>70.26000000000001</v>
+        <v>17.13</v>
       </c>
       <c r="L2" t="n">
-        <v>71.27</v>
+        <v>17.33</v>
       </c>
       <c r="M2" t="n">
-        <v>71.78</v>
+        <v>18.04</v>
       </c>
       <c r="N2" t="n">
-        <v>54.01</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="3">
@@ -518,43 +518,43 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1489</v>
+        <v>0.0046915</v>
       </c>
       <c r="D3" t="n">
-        <v>77.13</v>
+        <v>4.18</v>
       </c>
       <c r="E3" t="n">
-        <v>57.08</v>
+        <v>5.47</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>7.29</v>
       </c>
       <c r="G3" t="n">
-        <v>14.83</v>
+        <v>10.84</v>
       </c>
       <c r="H3" t="n">
-        <v>7.42</v>
+        <v>11.68</v>
       </c>
       <c r="I3" t="n">
-        <v>1.48</v>
+        <v>13.62</v>
       </c>
       <c r="J3" t="n">
-        <v>4.31</v>
+        <v>15.9</v>
       </c>
       <c r="K3" t="n">
-        <v>14.17</v>
+        <v>17.42</v>
       </c>
       <c r="L3" t="n">
-        <v>14.17</v>
+        <v>17.62</v>
       </c>
       <c r="M3" t="n">
-        <v>12.82</v>
+        <v>18.33</v>
       </c>
       <c r="N3" t="n">
-        <v>25.34</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="4">
@@ -562,43 +562,43 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15261</v>
+        <v>0.001235</v>
       </c>
       <c r="D4" t="n">
-        <v>76.06</v>
+        <v>4.46</v>
       </c>
       <c r="E4" t="n">
-        <v>56.12</v>
+        <v>5.75</v>
       </c>
       <c r="F4" t="n">
-        <v>49.09</v>
+        <v>7.56</v>
       </c>
       <c r="G4" t="n">
-        <v>14.13</v>
+        <v>11.1</v>
       </c>
       <c r="H4" t="n">
-        <v>6.77</v>
+        <v>11.93</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08</v>
+        <v>13.87</v>
       </c>
       <c r="J4" t="n">
-        <v>4.89</v>
+        <v>16.14</v>
       </c>
       <c r="K4" t="n">
-        <v>14.7</v>
+        <v>17.66</v>
       </c>
       <c r="L4" t="n">
-        <v>14.7</v>
+        <v>17.86</v>
       </c>
       <c r="M4" t="n">
-        <v>13.36</v>
+        <v>18.56</v>
       </c>
       <c r="N4" t="n">
-        <v>25.19</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="5">
@@ -606,43 +606,43 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>0.058318</v>
+        <v>0.00011877</v>
       </c>
       <c r="D5" t="n">
-        <v>30.91</v>
+        <v>5.31</v>
       </c>
       <c r="E5" t="n">
-        <v>16.09</v>
+        <v>6.58</v>
       </c>
       <c r="F5" t="n">
-        <v>10.86</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>15.13</v>
+        <v>11.9</v>
       </c>
       <c r="H5" t="n">
-        <v>20.61</v>
+        <v>12.72</v>
       </c>
       <c r="I5" t="n">
-        <v>27.18</v>
+        <v>14.64</v>
       </c>
       <c r="J5" t="n">
-        <v>29.28</v>
+        <v>16.89</v>
       </c>
       <c r="K5" t="n">
-        <v>36.57</v>
+        <v>18.39</v>
       </c>
       <c r="L5" t="n">
-        <v>36.57</v>
+        <v>18.59</v>
       </c>
       <c r="M5" t="n">
-        <v>35.57</v>
+        <v>19.29</v>
       </c>
       <c r="N5" t="n">
-        <v>25.88</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="6">
@@ -650,43 +650,43 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>0.058473</v>
+        <v>0.0014375</v>
       </c>
       <c r="D6" t="n">
-        <v>29.76</v>
+        <v>5.09</v>
       </c>
       <c r="E6" t="n">
-        <v>15.07</v>
+        <v>6.36</v>
       </c>
       <c r="F6" t="n">
-        <v>9.890000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="G6" t="n">
-        <v>15.88</v>
+        <v>11.67</v>
       </c>
       <c r="H6" t="n">
-        <v>21.31</v>
+        <v>12.5</v>
       </c>
       <c r="I6" t="n">
-        <v>27.82</v>
+        <v>14.42</v>
       </c>
       <c r="J6" t="n">
-        <v>29.9</v>
+        <v>16.68</v>
       </c>
       <c r="K6" t="n">
-        <v>37.13</v>
+        <v>18.18</v>
       </c>
       <c r="L6" t="n">
-        <v>37.13</v>
+        <v>18.38</v>
       </c>
       <c r="M6" t="n">
-        <v>36.14</v>
+        <v>19.09</v>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="7">
@@ -694,43 +694,43 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>0.058693</v>
+        <v>0.0039965</v>
       </c>
       <c r="D7" t="n">
-        <v>28.64</v>
+        <v>3.99</v>
       </c>
       <c r="E7" t="n">
-        <v>14.08</v>
+        <v>5.25</v>
       </c>
       <c r="F7" t="n">
-        <v>8.94</v>
+        <v>7.06</v>
       </c>
       <c r="G7" t="n">
-        <v>16.61</v>
+        <v>10.62</v>
       </c>
       <c r="H7" t="n">
-        <v>21.99</v>
+        <v>11.45</v>
       </c>
       <c r="I7" t="n">
-        <v>28.45</v>
+        <v>13.4</v>
       </c>
       <c r="J7" t="n">
-        <v>30.51</v>
+        <v>15.68</v>
       </c>
       <c r="K7" t="n">
-        <v>37.67</v>
+        <v>17.2</v>
       </c>
       <c r="L7" t="n">
-        <v>37.67</v>
+        <v>17.4</v>
       </c>
       <c r="M7" t="n">
-        <v>36.69</v>
+        <v>18.11</v>
       </c>
       <c r="N7" t="n">
-        <v>26.12</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="8">
@@ -738,43 +738,43 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>0.058209</v>
+        <v>0.0028017</v>
       </c>
       <c r="D8" t="n">
-        <v>28.65</v>
+        <v>2.28</v>
       </c>
       <c r="E8" t="n">
-        <v>14.08</v>
+        <v>3.3</v>
       </c>
       <c r="F8" t="n">
-        <v>8.94</v>
+        <v>4.96</v>
       </c>
       <c r="G8" t="n">
-        <v>16.6</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>21.98</v>
+        <v>9.23</v>
       </c>
       <c r="I8" t="n">
-        <v>28.45</v>
+        <v>11.16</v>
       </c>
       <c r="J8" t="n">
-        <v>30.5</v>
+        <v>13.46</v>
       </c>
       <c r="K8" t="n">
-        <v>37.67</v>
+        <v>14.99</v>
       </c>
       <c r="L8" t="n">
-        <v>37.67</v>
+        <v>15.17</v>
       </c>
       <c r="M8" t="n">
-        <v>36.69</v>
+        <v>15.88</v>
       </c>
       <c r="N8" t="n">
-        <v>26.12</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -782,43 +782,43 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>0.057775</v>
+        <v>0.0036963</v>
       </c>
       <c r="D9" t="n">
-        <v>29.37</v>
+        <v>1.86</v>
       </c>
       <c r="E9" t="n">
-        <v>14.73</v>
+        <v>2.78</v>
       </c>
       <c r="F9" t="n">
-        <v>9.56</v>
+        <v>4.36</v>
       </c>
       <c r="G9" t="n">
-        <v>16.13</v>
+        <v>7.81</v>
       </c>
       <c r="H9" t="n">
-        <v>21.54</v>
+        <v>8.52</v>
       </c>
       <c r="I9" t="n">
-        <v>28.04</v>
+        <v>10.43</v>
       </c>
       <c r="J9" t="n">
-        <v>30.11</v>
+        <v>12.71</v>
       </c>
       <c r="K9" t="n">
-        <v>37.32</v>
+        <v>14.22</v>
       </c>
       <c r="L9" t="n">
-        <v>37.32</v>
+        <v>14.39</v>
       </c>
       <c r="M9" t="n">
-        <v>36.33</v>
+        <v>15.1</v>
       </c>
       <c r="N9" t="n">
-        <v>26.04</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -826,43 +826,43 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05827</v>
+        <v>0.0043385</v>
       </c>
       <c r="D10" t="n">
-        <v>29.28</v>
+        <v>1.51</v>
       </c>
       <c r="E10" t="n">
-        <v>14.64</v>
+        <v>2.33</v>
       </c>
       <c r="F10" t="n">
-        <v>9.48</v>
+        <v>3.83</v>
       </c>
       <c r="G10" t="n">
-        <v>16.19</v>
+        <v>7.24</v>
       </c>
       <c r="H10" t="n">
-        <v>21.6</v>
+        <v>7.89</v>
       </c>
       <c r="I10" t="n">
-        <v>28.09</v>
+        <v>9.76</v>
       </c>
       <c r="J10" t="n">
-        <v>30.16</v>
+        <v>12.02</v>
       </c>
       <c r="K10" t="n">
-        <v>37.36</v>
+        <v>13.51</v>
       </c>
       <c r="L10" t="n">
-        <v>37.36</v>
+        <v>13.65</v>
       </c>
       <c r="M10" t="n">
-        <v>36.38</v>
+        <v>14.35</v>
       </c>
       <c r="N10" t="n">
-        <v>26.05</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -870,43 +870,43 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>0.057986</v>
+        <v>0.001164</v>
       </c>
       <c r="D11" t="n">
-        <v>29.66</v>
+        <v>0.38</v>
       </c>
       <c r="E11" t="n">
-        <v>14.98</v>
+        <v>0.59</v>
       </c>
       <c r="F11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="G11" t="n">
-        <v>15.95</v>
+        <v>4.51</v>
       </c>
       <c r="H11" t="n">
-        <v>21.37</v>
+        <v>4.72</v>
       </c>
       <c r="I11" t="n">
-        <v>27.88</v>
+        <v>6.24</v>
       </c>
       <c r="J11" t="n">
-        <v>29.96</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>37.18</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>37.18</v>
+        <v>9.33</v>
       </c>
       <c r="M11" t="n">
-        <v>36.19</v>
+        <v>9.81</v>
       </c>
       <c r="N11" t="n">
-        <v>26.01</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="12">
@@ -914,43 +914,43 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00095341</v>
+        <v>0.0076323</v>
       </c>
       <c r="D12" t="n">
-        <v>14.44</v>
+        <v>0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="n">
-        <v>3.09</v>
+        <v>2.52</v>
       </c>
       <c r="G12" t="n">
-        <v>25.81</v>
+        <v>5.71</v>
       </c>
       <c r="H12" t="n">
-        <v>30.6</v>
+        <v>6.13</v>
       </c>
       <c r="I12" t="n">
-        <v>36.35</v>
+        <v>7.82</v>
       </c>
       <c r="J12" t="n">
-        <v>38.18</v>
+        <v>9.94</v>
       </c>
       <c r="K12" t="n">
-        <v>44.55</v>
+        <v>11.32</v>
       </c>
       <c r="L12" t="n">
-        <v>44.55</v>
+        <v>11.32</v>
       </c>
       <c r="M12" t="n">
-        <v>43.68</v>
+        <v>11.9</v>
       </c>
       <c r="N12" t="n">
-        <v>28.27</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="13">
@@ -958,43 +958,43 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0011694</v>
+        <v>0.012627</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34</v>
+        <v>0.14</v>
       </c>
       <c r="E13" t="n">
-        <v>2.28</v>
+        <v>0.36</v>
       </c>
       <c r="F13" t="n">
-        <v>2.32</v>
+        <v>1.28</v>
       </c>
       <c r="G13" t="n">
-        <v>25.23</v>
+        <v>4.21</v>
       </c>
       <c r="H13" t="n">
-        <v>30.05</v>
+        <v>4.34</v>
       </c>
       <c r="I13" t="n">
-        <v>35.85</v>
+        <v>5.78</v>
       </c>
       <c r="J13" t="n">
-        <v>37.69</v>
+        <v>7.68</v>
       </c>
       <c r="K13" t="n">
-        <v>44.11</v>
+        <v>8.83</v>
       </c>
       <c r="L13" t="n">
-        <v>44.11</v>
+        <v>8.59</v>
       </c>
       <c r="M13" t="n">
-        <v>43.24</v>
+        <v>8.98</v>
       </c>
       <c r="N13" t="n">
-        <v>28.02</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="14">
@@ -1002,43 +1002,615 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.011659</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0078279</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="M15" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7.08</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>19</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.23841</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="F16" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="G16" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="H16" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="K16" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="M16" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>18.01</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.23917</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="H17" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="I17" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="K17" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="L17" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="M17" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17.91</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>21</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.044466</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="I18" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="J18" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="N18" t="n">
+        <v>15.06</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>22</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.047084</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="H19" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="I19" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="M19" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="N19" t="n">
+        <v>15.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>23</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.09234199999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="I20" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="K20" t="n">
+        <v>21</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="M20" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="N20" t="n">
+        <v>16.04</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.052423</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="H21" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I21" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="M21" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="N21" t="n">
+        <v>15.39</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.094012</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="J22" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="K22" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="L22" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="M22" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="N22" t="n">
+        <v>16.13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>26</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.15101</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="I23" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="K23" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="N23" t="n">
+        <v>16.91</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>27</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.19215</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="I24" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="J24" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="K24" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16.45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>28</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.061252</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="J25" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="K25" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>14.35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>29</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.15097</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="H26" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="J26" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="K26" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="M26" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="N26" t="n">
+        <v>17.01</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
         <v>30</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.0011615</v>
-      </c>
-      <c r="D14" t="n">
-        <v>13</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="G14" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="H14" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="I14" t="n">
-        <v>37.15</v>
-      </c>
-      <c r="J14" t="n">
-        <v>38.95</v>
-      </c>
-      <c r="K14" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="L14" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="M14" t="n">
-        <v>44.39</v>
-      </c>
-      <c r="N14" t="n">
-        <v>28.67</v>
+      <c r="C27" t="n">
+        <v>0.12011</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="I27" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="J27" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="K27" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="L27" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="M27" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="N27" t="n">
+        <v>13.45</v>
       </c>
     </row>
   </sheetData>
